--- a/locations.xlsx
+++ b/locations.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://surreyac-my.sharepoint.com/personal/dc00955_surrey_ac_uk/Documents/Desktop/Sara_case_report/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://surreyac-my.sharepoint.com/personal/gg00642_surrey_ac_uk/Documents/Desktop/Actigraphy Sara/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{E6D12119-FB4D-4FE9-9E46-FB8EE3BD751A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9091666C-4DCA-4799-9880-21A8DB14DA2B}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="8_{E6D12119-FB4D-4FE9-9E46-FB8EE3BD751A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{431D4126-1C2E-400C-AF31-B3AA3EB06A05}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{EFCBCB45-B80B-40E7-AA5C-92C8A109E731}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{EFCBCB45-B80B-40E7-AA5C-92C8A109E731}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -77,7 +77,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -87,6 +87,12 @@
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -422,13 +428,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF315835-37CF-49FA-8676-001123126FFC}">
-  <dimension ref="A1:B554"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:B1106"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.08984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.33203125" style="5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -436,7 +442,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <v>44825</v>
       </c>
@@ -444,7 +450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>44826</v>
       </c>
@@ -452,7 +458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>44827</v>
       </c>
@@ -460,7 +466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>44828</v>
       </c>
@@ -468,7 +474,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>44829</v>
       </c>
@@ -476,7 +482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>44830</v>
       </c>
@@ -484,7 +490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
         <v>44831</v>
       </c>
@@ -492,7 +498,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>44832</v>
       </c>
@@ -500,7 +506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>44833</v>
       </c>
@@ -508,7 +514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>44834</v>
       </c>
@@ -516,7 +522,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>44835</v>
       </c>
@@ -524,7 +530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
         <v>44836</v>
       </c>
@@ -532,7 +538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>44837</v>
       </c>
@@ -540,7 +546,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <v>44838</v>
       </c>
@@ -548,7 +554,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
         <v>44839</v>
       </c>
@@ -556,7 +562,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
         <v>44840</v>
       </c>
@@ -564,7 +570,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
         <v>44841</v>
       </c>
@@ -572,7 +578,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
         <v>44842</v>
       </c>
@@ -580,7 +586,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
         <v>44843</v>
       </c>
@@ -588,7 +594,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
         <v>44844</v>
       </c>
@@ -596,7 +602,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3">
         <v>44845</v>
       </c>
@@ -604,7 +610,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3">
         <v>44846</v>
       </c>
@@ -612,7 +618,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3">
         <v>44847</v>
       </c>
@@ -620,7 +626,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3">
         <v>44848</v>
       </c>
@@ -628,7 +634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3">
         <v>44849</v>
       </c>
@@ -636,7 +642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A27" s="3">
         <v>44850</v>
       </c>
@@ -644,7 +650,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3">
         <v>44851</v>
       </c>
@@ -652,7 +658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A29" s="3">
         <v>44852</v>
       </c>
@@ -660,7 +666,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A30" s="3">
         <v>44853</v>
       </c>
@@ -668,7 +674,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A31" s="3">
         <v>44854</v>
       </c>
@@ -676,7 +682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A32" s="3">
         <v>44855</v>
       </c>
@@ -684,7 +690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A33" s="3">
         <v>44856</v>
       </c>
@@ -692,7 +698,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A34" s="3">
         <v>44857</v>
       </c>
@@ -700,7 +706,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A35" s="3">
         <v>44858</v>
       </c>
@@ -708,7 +714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A36" s="3">
         <v>44859</v>
       </c>
@@ -716,7 +722,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A37" s="3">
         <v>44860</v>
       </c>
@@ -724,7 +730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A38" s="3">
         <v>44861</v>
       </c>
@@ -732,7 +738,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A39" s="3">
         <v>44862</v>
       </c>
@@ -740,7 +746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A40" s="3">
         <v>44863</v>
       </c>
@@ -748,7 +754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A41" s="3">
         <v>44864</v>
       </c>
@@ -756,7 +762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A42" s="3">
         <v>44865</v>
       </c>
@@ -764,7 +770,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A43" s="3">
         <v>44866</v>
       </c>
@@ -772,7 +778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A44" s="3">
         <v>44867</v>
       </c>
@@ -780,7 +786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A45" s="3">
         <v>44868</v>
       </c>
@@ -788,7 +794,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A46" s="3">
         <v>44869</v>
       </c>
@@ -796,7 +802,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A47" s="3">
         <v>44870</v>
       </c>
@@ -804,7 +810,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A48" s="3">
         <v>44871</v>
       </c>
@@ -812,7 +818,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A49" s="3">
         <v>44872</v>
       </c>
@@ -820,7 +826,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A50" s="3">
         <v>44873</v>
       </c>
@@ -828,7 +834,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A51" s="3">
         <v>44874</v>
       </c>
@@ -836,7 +842,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A52" s="3">
         <v>44875</v>
       </c>
@@ -844,7 +850,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A53" s="3">
         <v>44876</v>
       </c>
@@ -852,7 +858,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A54" s="3">
         <v>44877</v>
       </c>
@@ -860,7 +866,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A55" s="3">
         <v>44878</v>
       </c>
@@ -868,7 +874,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A56" s="3">
         <v>44879</v>
       </c>
@@ -876,7 +882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A57" s="3">
         <v>44880</v>
       </c>
@@ -884,7 +890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A58" s="3">
         <v>44881</v>
       </c>
@@ -892,7 +898,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A59" s="3">
         <v>44882</v>
       </c>
@@ -900,7 +906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A60" s="3">
         <v>44883</v>
       </c>
@@ -908,7 +914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A61" s="3">
         <v>44884</v>
       </c>
@@ -916,7 +922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A62" s="3">
         <v>44885</v>
       </c>
@@ -924,7 +930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A63" s="3">
         <v>44886</v>
       </c>
@@ -932,7 +938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A64" s="3">
         <v>44887</v>
       </c>
@@ -940,7 +946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A65" s="3">
         <v>44888</v>
       </c>
@@ -948,7 +954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A66" s="3">
         <v>44889</v>
       </c>
@@ -956,7 +962,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A67" s="3">
         <v>44890</v>
       </c>
@@ -964,7 +970,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A68" s="3">
         <v>44891</v>
       </c>
@@ -972,7 +978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A69" s="3">
         <v>44892</v>
       </c>
@@ -980,7 +986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A70" s="3">
         <v>44893</v>
       </c>
@@ -988,7 +994,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A71" s="3">
         <v>44894</v>
       </c>
@@ -996,7 +1002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A72" s="3">
         <v>44895</v>
       </c>
@@ -1004,7 +1010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A73" s="3">
         <v>44896</v>
       </c>
@@ -1012,7 +1018,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A74" s="3">
         <v>44897</v>
       </c>
@@ -1020,7 +1026,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A75" s="3">
         <v>44898</v>
       </c>
@@ -1028,7 +1034,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A76" s="3">
         <v>44899</v>
       </c>
@@ -1036,7 +1042,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A77" s="3">
         <v>44900</v>
       </c>
@@ -1044,7 +1050,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A78" s="3">
         <v>44901</v>
       </c>
@@ -1052,7 +1058,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A79" s="3">
         <v>44902</v>
       </c>
@@ -1060,7 +1066,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A80" s="3">
         <v>44903</v>
       </c>
@@ -1068,7 +1074,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A81" s="3">
         <v>44904</v>
       </c>
@@ -1076,7 +1082,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A82" s="3">
         <v>44905</v>
       </c>
@@ -1084,7 +1090,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A83" s="3">
         <v>44906</v>
       </c>
@@ -1092,7 +1098,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A84" s="3">
         <v>44907</v>
       </c>
@@ -1100,7 +1106,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A85" s="3">
         <v>44908</v>
       </c>
@@ -1108,7 +1114,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A86" s="3">
         <v>44909</v>
       </c>
@@ -1116,7 +1122,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A87" s="3">
         <v>44910</v>
       </c>
@@ -1124,7 +1130,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A88" s="3">
         <v>44911</v>
       </c>
@@ -1132,7 +1138,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A89" s="3">
         <v>44912</v>
       </c>
@@ -1140,7 +1146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A90" s="3">
         <v>44913</v>
       </c>
@@ -1148,7 +1154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A91" s="3">
         <v>44914</v>
       </c>
@@ -1156,7 +1162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A92" s="3">
         <v>44915</v>
       </c>
@@ -1164,7 +1170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A93" s="3">
         <v>44916</v>
       </c>
@@ -1172,7 +1178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A94" s="3">
         <v>44917</v>
       </c>
@@ -1180,7 +1186,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A95" s="3">
         <v>44918</v>
       </c>
@@ -1188,7 +1194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A96" s="3">
         <v>44919</v>
       </c>
@@ -1196,7 +1202,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A97" s="3">
         <v>44920</v>
       </c>
@@ -1204,7 +1210,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A98" s="3">
         <v>44921</v>
       </c>
@@ -1212,7 +1218,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A99" s="3">
         <v>44922</v>
       </c>
@@ -1220,7 +1226,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A100" s="3">
         <v>44923</v>
       </c>
@@ -1228,7 +1234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A101" s="3">
         <v>44924</v>
       </c>
@@ -1236,7 +1242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A102" s="3">
         <v>44925</v>
       </c>
@@ -1244,7 +1250,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A103" s="3">
         <v>44926</v>
       </c>
@@ -1252,7 +1258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A104" s="3">
         <v>44927</v>
       </c>
@@ -1260,7 +1266,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A105" s="3">
         <v>44928</v>
       </c>
@@ -1268,7 +1274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A106" s="3">
         <v>44929</v>
       </c>
@@ -1276,7 +1282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A107" s="3">
         <v>44930</v>
       </c>
@@ -1284,7 +1290,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A108" s="3">
         <v>44931</v>
       </c>
@@ -1292,7 +1298,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A109" s="3">
         <v>44932</v>
       </c>
@@ -1300,7 +1306,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A110" s="3">
         <v>44933</v>
       </c>
@@ -1308,7 +1314,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A111" s="3">
         <v>44934</v>
       </c>
@@ -1316,7 +1322,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A112" s="3">
         <v>44935</v>
       </c>
@@ -1324,7 +1330,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A113" s="3">
         <v>44936</v>
       </c>
@@ -1332,7 +1338,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A114" s="3">
         <v>44937</v>
       </c>
@@ -1340,7 +1346,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A115" s="3">
         <v>44938</v>
       </c>
@@ -1348,7 +1354,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A116" s="3">
         <v>44939</v>
       </c>
@@ -1356,7 +1362,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A117" s="3">
         <v>44940</v>
       </c>
@@ -1364,7 +1370,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A118" s="3">
         <v>44941</v>
       </c>
@@ -1372,7 +1378,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A119" s="3">
         <v>44942</v>
       </c>
@@ -1380,7 +1386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A120" s="3">
         <v>44943</v>
       </c>
@@ -1388,7 +1394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A121" s="3">
         <v>44944</v>
       </c>
@@ -1396,7 +1402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A122" s="3">
         <v>44945</v>
       </c>
@@ -1404,7 +1410,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A123" s="3">
         <v>44946</v>
       </c>
@@ -1412,7 +1418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A124" s="3">
         <v>44947</v>
       </c>
@@ -1420,7 +1426,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A125" s="3">
         <v>44948</v>
       </c>
@@ -1428,7 +1434,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A126" s="3">
         <v>44949</v>
       </c>
@@ -1436,7 +1442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A127" s="3">
         <v>44950</v>
       </c>
@@ -1444,7 +1450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A128" s="3">
         <v>44951</v>
       </c>
@@ -1452,7 +1458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A129" s="3">
         <v>44952</v>
       </c>
@@ -1460,7 +1466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A130" s="3">
         <v>44953</v>
       </c>
@@ -1468,7 +1474,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A131" s="3">
         <v>44954</v>
       </c>
@@ -1476,7 +1482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A132" s="3">
         <v>44955</v>
       </c>
@@ -1484,7 +1490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A133" s="3">
         <v>44956</v>
       </c>
@@ -1492,7 +1498,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A134" s="3">
         <v>44957</v>
       </c>
@@ -1500,7 +1506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A135" s="3">
         <v>44958</v>
       </c>
@@ -1508,7 +1514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A136" s="3">
         <v>44959</v>
       </c>
@@ -1516,7 +1522,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A137" s="3">
         <v>44960</v>
       </c>
@@ -1524,7 +1530,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A138" s="3">
         <v>44961</v>
       </c>
@@ -1532,7 +1538,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A139" s="3">
         <v>44962</v>
       </c>
@@ -1540,7 +1546,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A140" s="3">
         <v>44963</v>
       </c>
@@ -1548,7 +1554,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A141" s="3">
         <v>44964</v>
       </c>
@@ -1556,7 +1562,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A142" s="3">
         <v>44965</v>
       </c>
@@ -1564,7 +1570,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A143" s="3">
         <v>44966</v>
       </c>
@@ -1572,7 +1578,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A144" s="3">
         <v>44967</v>
       </c>
@@ -1580,7 +1586,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A145" s="3">
         <v>44968</v>
       </c>
@@ -1588,7 +1594,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A146" s="3">
         <v>44969</v>
       </c>
@@ -1596,7 +1602,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A147" s="3">
         <v>44970</v>
       </c>
@@ -1604,7 +1610,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A148" s="3">
         <v>44971</v>
       </c>
@@ -1612,7 +1618,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A149" s="3">
         <v>44972</v>
       </c>
@@ -1620,7 +1626,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A150" s="3">
         <v>44973</v>
       </c>
@@ -1628,7 +1634,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A151" s="3">
         <v>44974</v>
       </c>
@@ -1636,7 +1642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A152" s="3">
         <v>44975</v>
       </c>
@@ -1644,7 +1650,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A153" s="3">
         <v>44976</v>
       </c>
@@ -1652,7 +1658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A154" s="3">
         <v>44977</v>
       </c>
@@ -1660,7 +1666,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A155" s="3">
         <v>44978</v>
       </c>
@@ -1668,7 +1674,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A156" s="3">
         <v>44979</v>
       </c>
@@ -1676,7 +1682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A157" s="3">
         <v>44980</v>
       </c>
@@ -1684,7 +1690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A158" s="3">
         <v>44981</v>
       </c>
@@ -1692,7 +1698,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A159" s="3">
         <v>44982</v>
       </c>
@@ -1700,7 +1706,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A160" s="3">
         <v>44983</v>
       </c>
@@ -1708,7 +1714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A161" s="3">
         <v>44984</v>
       </c>
@@ -1716,7 +1722,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A162" s="3">
         <v>44985</v>
       </c>
@@ -1724,7 +1730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A163" s="3">
         <v>44986</v>
       </c>
@@ -1732,7 +1738,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A164" s="3">
         <v>44987</v>
       </c>
@@ -1740,7 +1746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A165" s="3">
         <v>44988</v>
       </c>
@@ -1748,7 +1754,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A166" s="3">
         <v>44989</v>
       </c>
@@ -1756,7 +1762,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A167" s="3">
         <v>44990</v>
       </c>
@@ -1764,7 +1770,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="168" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A168" s="3">
         <v>44991</v>
       </c>
@@ -1772,7 +1778,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="169" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A169" s="3">
         <v>44992</v>
       </c>
@@ -1780,7 +1786,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="170" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A170" s="3">
         <v>44993</v>
       </c>
@@ -1788,7 +1794,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="171" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A171" s="3">
         <v>44994</v>
       </c>
@@ -1796,7 +1802,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="172" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A172" s="3">
         <v>44995</v>
       </c>
@@ -1804,7 +1810,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="173" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A173" s="3">
         <v>44996</v>
       </c>
@@ -1812,7 +1818,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="174" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A174" s="3">
         <v>44997</v>
       </c>
@@ -1820,7 +1826,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="175" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A175" s="3">
         <v>44998</v>
       </c>
@@ -1828,7 +1834,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="176" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A176" s="3">
         <v>44999</v>
       </c>
@@ -1836,7 +1842,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A177" s="3">
         <v>45000</v>
       </c>
@@ -1844,7 +1850,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="178" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A178" s="3">
         <v>45001</v>
       </c>
@@ -1852,7 +1858,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A179" s="3">
         <v>45002</v>
       </c>
@@ -1860,7 +1866,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="180" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A180" s="3">
         <v>45003</v>
       </c>
@@ -1868,7 +1874,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="181" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A181" s="3">
         <v>45004</v>
       </c>
@@ -1876,7 +1882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A182" s="3">
         <v>45005</v>
       </c>
@@ -1884,7 +1890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A183" s="3">
         <v>45006</v>
       </c>
@@ -1892,7 +1898,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A184" s="3">
         <v>45007</v>
       </c>
@@ -1900,7 +1906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A185" s="3">
         <v>45008</v>
       </c>
@@ -1908,7 +1914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A186" s="3">
         <v>45009</v>
       </c>
@@ -1916,7 +1922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A187" s="3">
         <v>45010</v>
       </c>
@@ -1924,7 +1930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A188" s="3">
         <v>45011</v>
       </c>
@@ -1932,7 +1938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A189" s="3">
         <v>45012</v>
       </c>
@@ -1940,7 +1946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A190" s="3">
         <v>45013</v>
       </c>
@@ -1948,7 +1954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A191" s="3">
         <v>45014</v>
       </c>
@@ -1956,7 +1962,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A192" s="3">
         <v>45015</v>
       </c>
@@ -1964,7 +1970,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A193" s="3">
         <v>45016</v>
       </c>
@@ -1972,7 +1978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A194" s="3">
         <v>45017</v>
       </c>
@@ -1980,7 +1986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A195" s="3">
         <v>45018</v>
       </c>
@@ -1988,7 +1994,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A196" s="3">
         <v>45019</v>
       </c>
@@ -1996,7 +2002,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="197" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A197" s="3">
         <v>45020</v>
       </c>
@@ -2004,7 +2010,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="198" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A198" s="3">
         <v>45021</v>
       </c>
@@ -2012,7 +2018,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="199" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A199" s="3">
         <v>45022</v>
       </c>
@@ -2020,7 +2026,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="200" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A200" s="3">
         <v>45023</v>
       </c>
@@ -2028,7 +2034,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="201" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A201" s="3">
         <v>45024</v>
       </c>
@@ -2036,7 +2042,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="202" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A202" s="3">
         <v>45025</v>
       </c>
@@ -2044,7 +2050,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="203" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A203" s="3">
         <v>45026</v>
       </c>
@@ -2052,7 +2058,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="204" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A204" s="3">
         <v>45027</v>
       </c>
@@ -2060,7 +2066,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="205" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A205" s="3">
         <v>45028</v>
       </c>
@@ -2068,7 +2074,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="206" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A206" s="3">
         <v>45029</v>
       </c>
@@ -2076,7 +2082,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="207" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A207" s="3">
         <v>45030</v>
       </c>
@@ -2084,7 +2090,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="208" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A208" s="3">
         <v>45031</v>
       </c>
@@ -2092,7 +2098,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="209" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A209" s="3">
         <v>45032</v>
       </c>
@@ -2100,7 +2106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A210" s="3">
         <v>45033</v>
       </c>
@@ -2108,7 +2114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A211" s="3">
         <v>45034</v>
       </c>
@@ -2116,7 +2122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A212" s="3">
         <v>45035</v>
       </c>
@@ -2124,7 +2130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A213" s="3">
         <v>45036</v>
       </c>
@@ -2132,7 +2138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A214" s="3">
         <v>45037</v>
       </c>
@@ -2140,7 +2146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A215" s="3">
         <v>45038</v>
       </c>
@@ -2148,7 +2154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A216" s="3">
         <v>45039</v>
       </c>
@@ -2156,7 +2162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A217" s="3">
         <v>45040</v>
       </c>
@@ -2164,7 +2170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A218" s="3">
         <v>45041</v>
       </c>
@@ -2172,7 +2178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A219" s="3">
         <v>45042</v>
       </c>
@@ -2180,7 +2186,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A220" s="3">
         <v>45043</v>
       </c>
@@ -2188,7 +2194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A221" s="3">
         <v>45044</v>
       </c>
@@ -2196,7 +2202,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A222" s="3">
         <v>45045</v>
       </c>
@@ -2204,7 +2210,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A223" s="3">
         <v>45046</v>
       </c>
@@ -2212,7 +2218,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A224" s="3">
         <v>45047</v>
       </c>
@@ -2220,7 +2226,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A225" s="3">
         <v>45048</v>
       </c>
@@ -2228,7 +2234,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="226" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A226" s="3">
         <v>45049</v>
       </c>
@@ -2236,7 +2242,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="227" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A227" s="3">
         <v>45050</v>
       </c>
@@ -2244,7 +2250,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="228" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A228" s="3">
         <v>45051</v>
       </c>
@@ -2252,7 +2258,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="229" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A229" s="3">
         <v>45052</v>
       </c>
@@ -2260,7 +2266,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="230" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A230" s="3">
         <v>45053</v>
       </c>
@@ -2268,7 +2274,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="231" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A231" s="3">
         <v>45054</v>
       </c>
@@ -2276,7 +2282,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="232" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A232" s="3">
         <v>45055</v>
       </c>
@@ -2284,7 +2290,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="233" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A233" s="3">
         <v>45056</v>
       </c>
@@ -2292,7 +2298,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="234" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A234" s="3">
         <v>45057</v>
       </c>
@@ -2300,7 +2306,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="235" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A235" s="3">
         <v>45058</v>
       </c>
@@ -2308,7 +2314,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="236" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A236" s="3">
         <v>45059</v>
       </c>
@@ -2316,7 +2322,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="237" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A237" s="3">
         <v>45060</v>
       </c>
@@ -2324,7 +2330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="238" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A238" s="3">
         <v>45061</v>
       </c>
@@ -2332,7 +2338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="239" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A239" s="3">
         <v>45062</v>
       </c>
@@ -2340,7 +2346,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A240" s="3">
         <v>45063</v>
       </c>
@@ -2348,7 +2354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="241" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A241" s="3">
         <v>45064</v>
       </c>
@@ -2356,7 +2362,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="242" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A242" s="3">
         <v>45065</v>
       </c>
@@ -2364,7 +2370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A243" s="3">
         <v>45066</v>
       </c>
@@ -2372,7 +2378,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A244" s="3">
         <v>45067</v>
       </c>
@@ -2380,7 +2386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="245" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A245" s="3">
         <v>45068</v>
       </c>
@@ -2388,7 +2394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="246" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A246" s="3">
         <v>45069</v>
       </c>
@@ -2396,7 +2402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="247" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A247" s="3">
         <v>45070</v>
       </c>
@@ -2404,7 +2410,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="248" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A248" s="3">
         <v>45071</v>
       </c>
@@ -2412,7 +2418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A249" s="3">
         <v>45072</v>
       </c>
@@ -2420,7 +2426,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="250" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A250" s="3">
         <v>45073</v>
       </c>
@@ -2428,7 +2434,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="251" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A251" s="3">
         <v>45074</v>
       </c>
@@ -2436,7 +2442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A252" s="3">
         <v>45075</v>
       </c>
@@ -2444,7 +2450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="253" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A253" s="3">
         <v>45076</v>
       </c>
@@ -2452,7 +2458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A254" s="3">
         <v>45077</v>
       </c>
@@ -2460,7 +2466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="255" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A255" s="3">
         <v>45078</v>
       </c>
@@ -2468,7 +2474,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="256" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A256" s="3">
         <v>45079</v>
       </c>
@@ -2476,7 +2482,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="257" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A257" s="3">
         <v>45080</v>
       </c>
@@ -2484,7 +2490,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="258" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A258" s="3">
         <v>45081</v>
       </c>
@@ -2492,7 +2498,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="259" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A259" s="3">
         <v>45082</v>
       </c>
@@ -2500,7 +2506,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="260" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A260" s="3">
         <v>45083</v>
       </c>
@@ -2508,7 +2514,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="261" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A261" s="3">
         <v>45084</v>
       </c>
@@ -2516,7 +2522,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="262" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A262" s="3">
         <v>45085</v>
       </c>
@@ -2524,7 +2530,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="263" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A263" s="3">
         <v>45086</v>
       </c>
@@ -2532,7 +2538,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="264" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A264" s="3">
         <v>45087</v>
       </c>
@@ -2540,7 +2546,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="265" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A265" s="3">
         <v>45088</v>
       </c>
@@ -2548,7 +2554,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="266" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A266" s="3">
         <v>45089</v>
       </c>
@@ -2556,7 +2562,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="267" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A267" s="3">
         <v>45090</v>
       </c>
@@ -2564,7 +2570,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="268" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A268" s="3">
         <v>45091</v>
       </c>
@@ -2572,7 +2578,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="269" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A269" s="3">
         <v>45092</v>
       </c>
@@ -2580,7 +2586,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="270" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A270" s="3">
         <v>45093</v>
       </c>
@@ -2588,7 +2594,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="271" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A271" s="3">
         <v>45094</v>
       </c>
@@ -2596,7 +2602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="272" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A272" s="3">
         <v>45095</v>
       </c>
@@ -2604,7 +2610,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="273" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A273" s="3">
         <v>45096</v>
       </c>
@@ -2612,7 +2618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="274" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A274" s="3">
         <v>45097</v>
       </c>
@@ -2620,7 +2626,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="275" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A275" s="3">
         <v>45098</v>
       </c>
@@ -2628,7 +2634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="276" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A276" s="3">
         <v>45099</v>
       </c>
@@ -2636,7 +2642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="277" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A277" s="3">
         <v>45100</v>
       </c>
@@ -2644,7 +2650,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="278" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A278" s="3">
         <v>45101</v>
       </c>
@@ -2652,7 +2658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="279" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A279" s="3">
         <v>45102</v>
       </c>
@@ -2660,7 +2666,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="280" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A280" s="3">
         <v>45103</v>
       </c>
@@ -2668,7 +2674,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="281" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A281" s="3">
         <v>45104</v>
       </c>
@@ -2676,7 +2682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="282" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A282" s="3">
         <v>45105</v>
       </c>
@@ -2684,7 +2690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="283" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A283" s="3">
         <v>45106</v>
       </c>
@@ -2692,7 +2698,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="284" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A284" s="3">
         <v>45107</v>
       </c>
@@ -2700,7 +2706,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="285" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A285" s="3">
         <v>45108</v>
       </c>
@@ -2708,7 +2714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="286" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A286" s="3">
         <v>45109</v>
       </c>
@@ -2716,7 +2722,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="287" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A287" s="3">
         <v>45110</v>
       </c>
@@ -2724,7 +2730,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="288" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A288" s="3">
         <v>45111</v>
       </c>
@@ -2732,7 +2738,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="289" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A289" s="3">
         <v>45112</v>
       </c>
@@ -2740,7 +2746,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="290" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A290" s="3">
         <v>45113</v>
       </c>
@@ -2748,7 +2754,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="291" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A291" s="3">
         <v>45114</v>
       </c>
@@ -2756,7 +2762,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="292" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A292" s="3">
         <v>45115</v>
       </c>
@@ -2764,7 +2770,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="293" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A293" s="3">
         <v>45116</v>
       </c>
@@ -2772,7 +2778,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="294" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A294" s="3">
         <v>45117</v>
       </c>
@@ -2780,7 +2786,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="295" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A295" s="3">
         <v>45118</v>
       </c>
@@ -2788,7 +2794,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="296" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A296" s="3">
         <v>45119</v>
       </c>
@@ -2796,7 +2802,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="297" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A297" s="3">
         <v>45120</v>
       </c>
@@ -2804,7 +2810,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="298" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A298" s="3">
         <v>45121</v>
       </c>
@@ -2812,7 +2818,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="299" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A299" s="3">
         <v>45122</v>
       </c>
@@ -2820,7 +2826,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="300" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A300" s="3">
         <v>45123</v>
       </c>
@@ -2828,7 +2834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="301" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A301" s="3">
         <v>45124</v>
       </c>
@@ -2836,7 +2842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="302" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A302" s="3">
         <v>45125</v>
       </c>
@@ -2844,7 +2850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="303" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A303" s="3">
         <v>45126</v>
       </c>
@@ -2852,7 +2858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="304" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A304" s="3">
         <v>45127</v>
       </c>
@@ -2860,7 +2866,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="305" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A305" s="3">
         <v>45128</v>
       </c>
@@ -2868,7 +2874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="306" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A306" s="3">
         <v>45129</v>
       </c>
@@ -2876,7 +2882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="307" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A307" s="3">
         <v>45130</v>
       </c>
@@ -2884,7 +2890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="308" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A308" s="3">
         <v>45131</v>
       </c>
@@ -2892,7 +2898,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="309" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A309" s="3">
         <v>45132</v>
       </c>
@@ -2900,7 +2906,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="310" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A310" s="3">
         <v>45133</v>
       </c>
@@ -2908,7 +2914,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="311" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A311" s="3">
         <v>45134</v>
       </c>
@@ -2916,7 +2922,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="312" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A312" s="3">
         <v>45135</v>
       </c>
@@ -2924,7 +2930,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="313" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A313" s="3">
         <v>45136</v>
       </c>
@@ -2932,7 +2938,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="314" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A314" s="3">
         <v>45137</v>
       </c>
@@ -2940,7 +2946,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="315" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A315" s="3">
         <v>45138</v>
       </c>
@@ -2948,7 +2954,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="316" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A316" s="3">
         <v>45139</v>
       </c>
@@ -2956,7 +2962,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="317" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A317" s="3">
         <v>45140</v>
       </c>
@@ -2964,7 +2970,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="318" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A318" s="3">
         <v>45141</v>
       </c>
@@ -2972,7 +2978,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="319" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A319" s="3">
         <v>45142</v>
       </c>
@@ -2980,7 +2986,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="320" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A320" s="3">
         <v>45143</v>
       </c>
@@ -2988,7 +2994,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="321" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A321" s="3">
         <v>45144</v>
       </c>
@@ -2996,7 +3002,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="322" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A322" s="3">
         <v>45145</v>
       </c>
@@ -3004,7 +3010,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="323" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A323" s="3">
         <v>45146</v>
       </c>
@@ -3012,7 +3018,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="324" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A324" s="3">
         <v>45147</v>
       </c>
@@ -3020,7 +3026,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="325" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A325" s="3">
         <v>45148</v>
       </c>
@@ -3028,7 +3034,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="326" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A326" s="3">
         <v>45149</v>
       </c>
@@ -3036,7 +3042,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="327" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A327" s="3">
         <v>45150</v>
       </c>
@@ -3044,7 +3050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="328" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A328" s="3">
         <v>45151</v>
       </c>
@@ -3052,7 +3058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="329" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A329" s="3">
         <v>45152</v>
       </c>
@@ -3060,7 +3066,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="330" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A330" s="3">
         <v>45153</v>
       </c>
@@ -3068,7 +3074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="331" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A331" s="3">
         <v>45154</v>
       </c>
@@ -3076,7 +3082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="332" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A332" s="3">
         <v>45155</v>
       </c>
@@ -3084,7 +3090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="333" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A333" s="3">
         <v>45156</v>
       </c>
@@ -3092,7 +3098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="334" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A334" s="3">
         <v>45157</v>
       </c>
@@ -3100,7 +3106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="335" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A335" s="3">
         <v>45158</v>
       </c>
@@ -3108,7 +3114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="336" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A336" s="3">
         <v>45159</v>
       </c>
@@ -3116,7 +3122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="337" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A337" s="3">
         <v>45160</v>
       </c>
@@ -3124,7 +3130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="338" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A338" s="3">
         <v>45161</v>
       </c>
@@ -3132,7 +3138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="339" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A339" s="3">
         <v>45162</v>
       </c>
@@ -3140,7 +3146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="340" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A340" s="3">
         <v>45163</v>
       </c>
@@ -3148,7 +3154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="341" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A341" s="3">
         <v>45164</v>
       </c>
@@ -3156,7 +3162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="342" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A342" s="3">
         <v>45165</v>
       </c>
@@ -3164,7 +3170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="343" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A343" s="3">
         <v>45166</v>
       </c>
@@ -3172,7 +3178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="344" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A344" s="3">
         <v>45167</v>
       </c>
@@ -3180,7 +3186,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="345" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A345" s="3">
         <v>45168</v>
       </c>
@@ -3188,7 +3194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="346" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A346" s="3">
         <v>45169</v>
       </c>
@@ -3196,7 +3202,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="347" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A347" s="3">
         <v>45170</v>
       </c>
@@ -3204,7 +3210,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="348" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A348" s="3">
         <v>45171</v>
       </c>
@@ -3212,7 +3218,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="349" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A349" s="3">
         <v>45172</v>
       </c>
@@ -3220,7 +3226,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="350" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A350" s="3">
         <v>45173</v>
       </c>
@@ -3228,7 +3234,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="351" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A351" s="3">
         <v>45174</v>
       </c>
@@ -3236,7 +3242,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="352" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A352" s="3">
         <v>45175</v>
       </c>
@@ -3244,7 +3250,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="353" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A353" s="3">
         <v>45176</v>
       </c>
@@ -3252,7 +3258,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="354" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A354" s="3">
         <v>45177</v>
       </c>
@@ -3260,7 +3266,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="355" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A355" s="3">
         <v>45178</v>
       </c>
@@ -3268,7 +3274,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="356" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A356" s="3">
         <v>45179</v>
       </c>
@@ -3276,7 +3282,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="357" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A357" s="3">
         <v>45180</v>
       </c>
@@ -3284,7 +3290,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="358" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A358" s="3">
         <v>45181</v>
       </c>
@@ -3292,7 +3298,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="359" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A359" s="3">
         <v>45182</v>
       </c>
@@ -3300,7 +3306,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="360" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A360" s="3">
         <v>45183</v>
       </c>
@@ -3308,7 +3314,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="361" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A361" s="3">
         <v>45184</v>
       </c>
@@ -3316,7 +3322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="362" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A362" s="3">
         <v>45185</v>
       </c>
@@ -3324,7 +3330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="363" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A363" s="3">
         <v>45186</v>
       </c>
@@ -3332,7 +3338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="364" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A364" s="3">
         <v>45187</v>
       </c>
@@ -3340,7 +3346,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="365" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A365" s="3">
         <v>45188</v>
       </c>
@@ -3348,7 +3354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="366" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A366" s="3">
         <v>45189</v>
       </c>
@@ -3356,7 +3362,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="367" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A367" s="3">
         <v>45190</v>
       </c>
@@ -3364,7 +3370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="368" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A368" s="3">
         <v>45191</v>
       </c>
@@ -3372,7 +3378,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="369" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A369" s="3">
         <v>45192</v>
       </c>
@@ -3380,7 +3386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="370" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A370" s="3">
         <v>45193</v>
       </c>
@@ -3388,7 +3394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="371" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A371" s="3">
         <v>45194</v>
       </c>
@@ -3396,7 +3402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="372" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A372" s="3">
         <v>45195</v>
       </c>
@@ -3404,7 +3410,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="373" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A373" s="3">
         <v>45196</v>
       </c>
@@ -3412,7 +3418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="374" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A374" s="3">
         <v>45197</v>
       </c>
@@ -3420,7 +3426,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="375" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A375" s="3">
         <v>45198</v>
       </c>
@@ -3428,7 +3434,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="376" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A376" s="3">
         <v>45199</v>
       </c>
@@ -3436,7 +3442,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="377" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A377" s="3">
         <v>45200</v>
       </c>
@@ -3444,7 +3450,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="378" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A378" s="3">
         <v>45201</v>
       </c>
@@ -3452,7 +3458,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="379" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A379" s="3">
         <v>45202</v>
       </c>
@@ -3460,7 +3466,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="380" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A380" s="3">
         <v>45203</v>
       </c>
@@ -3468,7 +3474,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="381" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A381" s="3">
         <v>45204</v>
       </c>
@@ -3476,7 +3482,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="382" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A382" s="3">
         <v>45205</v>
       </c>
@@ -3484,7 +3490,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="383" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A383" s="3">
         <v>45206</v>
       </c>
@@ -3492,7 +3498,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="384" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A384" s="3">
         <v>45207</v>
       </c>
@@ -3500,7 +3506,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="385" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A385" s="3">
         <v>45208</v>
       </c>
@@ -3508,7 +3514,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="386" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A386" s="3">
         <v>45209</v>
       </c>
@@ -3516,7 +3522,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="387" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A387" s="3">
         <v>45210</v>
       </c>
@@ -3524,7 +3530,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="388" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A388" s="3">
         <v>45211</v>
       </c>
@@ -3532,7 +3538,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="389" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A389" s="3">
         <v>45212</v>
       </c>
@@ -3540,7 +3546,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="390" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A390" s="3">
         <v>45213</v>
       </c>
@@ -3548,7 +3554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="391" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A391" s="3">
         <v>45214</v>
       </c>
@@ -3556,7 +3562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="392" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A392" s="3">
         <v>45215</v>
       </c>
@@ -3564,7 +3570,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="393" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A393" s="3">
         <v>45216</v>
       </c>
@@ -3572,7 +3578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="394" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A394" s="3">
         <v>45217</v>
       </c>
@@ -3580,7 +3586,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="395" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A395" s="3">
         <v>45218</v>
       </c>
@@ -3588,7 +3594,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="396" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A396" s="3">
         <v>45219</v>
       </c>
@@ -3596,7 +3602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="397" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A397" s="3">
         <v>45220</v>
       </c>
@@ -3604,7 +3610,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="398" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A398" s="3">
         <v>45221</v>
       </c>
@@ -3612,7 +3618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="399" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A399" s="3">
         <v>45222</v>
       </c>
@@ -3620,7 +3626,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="400" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A400" s="3">
         <v>45223</v>
       </c>
@@ -3628,7 +3634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="401" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A401" s="3">
         <v>45224</v>
       </c>
@@ -3636,7 +3642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="402" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A402" s="3">
         <v>45225</v>
       </c>
@@ -3644,7 +3650,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="403" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A403" s="3">
         <v>45226</v>
       </c>
@@ -3652,7 +3658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="404" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A404" s="3">
         <v>45227</v>
       </c>
@@ -3660,7 +3666,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="405" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A405" s="3">
         <v>45228</v>
       </c>
@@ -3668,7 +3674,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="406" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A406" s="3">
         <v>45229</v>
       </c>
@@ -3676,7 +3682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="407" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A407" s="3">
         <v>45230</v>
       </c>
@@ -3684,7 +3690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="408" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A408" s="3">
         <v>45231</v>
       </c>
@@ -3692,7 +3698,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="409" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A409" s="3">
         <v>45232</v>
       </c>
@@ -3700,7 +3706,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="410" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A410" s="3">
         <v>45233</v>
       </c>
@@ -3708,7 +3714,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="411" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A411" s="3">
         <v>45234</v>
       </c>
@@ -3716,7 +3722,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="412" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A412" s="3">
         <v>45235</v>
       </c>
@@ -3724,7 +3730,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="413" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A413" s="3">
         <v>45236</v>
       </c>
@@ -3732,7 +3738,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="414" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A414" s="3">
         <v>45237</v>
       </c>
@@ -3740,7 +3746,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="415" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A415" s="3">
         <v>45238</v>
       </c>
@@ -3748,7 +3754,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="416" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A416" s="3">
         <v>45239</v>
       </c>
@@ -3756,7 +3762,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="417" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A417" s="3">
         <v>45240</v>
       </c>
@@ -3764,7 +3770,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="418" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A418" s="3">
         <v>45241</v>
       </c>
@@ -3772,7 +3778,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="419" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A419" s="3">
         <v>45242</v>
       </c>
@@ -3780,7 +3786,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="420" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A420" s="3">
         <v>45243</v>
       </c>
@@ -3788,7 +3794,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="421" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A421" s="3">
         <v>45244</v>
       </c>
@@ -3796,7 +3802,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="422" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A422" s="3">
         <v>45245</v>
       </c>
@@ -3804,7 +3810,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="423" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A423" s="3">
         <v>45246</v>
       </c>
@@ -3812,7 +3818,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="424" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="424" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A424" s="3">
         <v>45247</v>
       </c>
@@ -3820,7 +3826,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="425" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="425" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A425" s="3">
         <v>45248</v>
       </c>
@@ -3828,7 +3834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="426" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="426" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A426" s="3">
         <v>45249</v>
       </c>
@@ -3836,7 +3842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="427" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="427" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A427" s="3">
         <v>45250</v>
       </c>
@@ -3844,7 +3850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="428" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="428" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A428" s="3">
         <v>45251</v>
       </c>
@@ -3852,7 +3858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="429" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="429" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A429" s="3">
         <v>45252</v>
       </c>
@@ -3860,7 +3866,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="430" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="430" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A430" s="3">
         <v>45253</v>
       </c>
@@ -3868,7 +3874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="431" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="431" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A431" s="3">
         <v>45254</v>
       </c>
@@ -3876,7 +3882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="432" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="432" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A432" s="3">
         <v>45255</v>
       </c>
@@ -3884,7 +3890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="433" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="433" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A433" s="3">
         <v>45256</v>
       </c>
@@ -3892,7 +3898,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="434" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A434" s="3">
         <v>45257</v>
       </c>
@@ -3900,7 +3906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="435" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="435" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A435" s="3">
         <v>45258</v>
       </c>
@@ -3908,7 +3914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="436" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="436" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A436" s="3">
         <v>45259</v>
       </c>
@@ -3916,7 +3922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="437" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="437" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A437" s="3">
         <v>45260</v>
       </c>
@@ -3924,7 +3930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="438" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="438" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A438" s="3">
         <v>45261</v>
       </c>
@@ -3932,7 +3938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="439" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="439" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A439" s="3">
         <v>45262</v>
       </c>
@@ -3940,7 +3946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="440" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="440" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A440" s="3">
         <v>45263</v>
       </c>
@@ -3948,7 +3954,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="441" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="441" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A441" s="3">
         <v>45264</v>
       </c>
@@ -3956,7 +3962,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="442" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="442" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A442" s="3">
         <v>45265</v>
       </c>
@@ -3964,7 +3970,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="443" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="443" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A443" s="3">
         <v>45266</v>
       </c>
@@ -3972,7 +3978,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="444" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="444" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A444" s="3">
         <v>45267</v>
       </c>
@@ -3980,7 +3986,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="445" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="445" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A445" s="3">
         <v>45268</v>
       </c>
@@ -3988,7 +3994,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="446" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="446" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A446" s="3">
         <v>45269</v>
       </c>
@@ -3996,7 +4002,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="447" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="447" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A447" s="3">
         <v>45270</v>
       </c>
@@ -4004,7 +4010,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="448" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="448" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A448" s="3">
         <v>45271</v>
       </c>
@@ -4012,7 +4018,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="449" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="449" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A449" s="3">
         <v>45272</v>
       </c>
@@ -4020,7 +4026,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="450" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="450" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A450" s="3">
         <v>45273</v>
       </c>
@@ -4028,7 +4034,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="451" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="451" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A451" s="3">
         <v>45274</v>
       </c>
@@ -4036,7 +4042,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="452" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="452" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A452" s="3">
         <v>45275</v>
       </c>
@@ -4044,7 +4050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="453" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="453" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A453" s="3">
         <v>45276</v>
       </c>
@@ -4052,7 +4058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="454" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="454" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A454" s="3">
         <v>45277</v>
       </c>
@@ -4060,7 +4066,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="455" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="455" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A455" s="3">
         <v>45278</v>
       </c>
@@ -4068,7 +4074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="456" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="456" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A456" s="3">
         <v>45279</v>
       </c>
@@ -4076,7 +4082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="457" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="457" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A457" s="3">
         <v>45280</v>
       </c>
@@ -4084,7 +4090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="458" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="458" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A458" s="3">
         <v>45281</v>
       </c>
@@ -4092,7 +4098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="459" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="459" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A459" s="3">
         <v>45282</v>
       </c>
@@ -4100,7 +4106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="460" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="460" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A460" s="3">
         <v>45283</v>
       </c>
@@ -4108,7 +4114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="461" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="461" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A461" s="3">
         <v>45284</v>
       </c>
@@ -4116,7 +4122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="462" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="462" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A462" s="3">
         <v>45285</v>
       </c>
@@ -4124,7 +4130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="463" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="463" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A463" s="3">
         <v>45286</v>
       </c>
@@ -4132,7 +4138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="464" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="464" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A464" s="3">
         <v>45287</v>
       </c>
@@ -4140,7 +4146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="465" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="465" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A465" s="3">
         <v>45288</v>
       </c>
@@ -4148,7 +4154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="466" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="466" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A466" s="3">
         <v>45289</v>
       </c>
@@ -4156,7 +4162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="467" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="467" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A467" s="3">
         <v>45290</v>
       </c>
@@ -4164,7 +4170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="468" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="468" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A468" s="3">
         <v>45291</v>
       </c>
@@ -4172,7 +4178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="469" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="469" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A469" s="3">
         <v>45292</v>
       </c>
@@ -4180,7 +4186,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="470" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="470" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A470" s="3">
         <v>45293</v>
       </c>
@@ -4188,7 +4194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="471" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="471" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A471" s="3">
         <v>45294</v>
       </c>
@@ -4196,7 +4202,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="472" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="472" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A472" s="3">
         <v>45295</v>
       </c>
@@ -4204,7 +4210,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="473" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="473" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A473" s="3">
         <v>45296</v>
       </c>
@@ -4212,7 +4218,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="474" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="474" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A474" s="3">
         <v>45297</v>
       </c>
@@ -4220,7 +4226,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="475" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="475" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A475" s="3">
         <v>45298</v>
       </c>
@@ -4228,7 +4234,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="476" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="476" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A476" s="3">
         <v>45299</v>
       </c>
@@ -4236,7 +4242,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="477" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="477" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A477" s="3">
         <v>45300</v>
       </c>
@@ -4244,7 +4250,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="478" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="478" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A478" s="3">
         <v>45301</v>
       </c>
@@ -4252,7 +4258,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="479" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="479" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A479" s="3">
         <v>45302</v>
       </c>
@@ -4260,7 +4266,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="480" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="480" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A480" s="3">
         <v>45303</v>
       </c>
@@ -4268,7 +4274,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="481" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="481" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A481" s="3">
         <v>45304</v>
       </c>
@@ -4276,7 +4282,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="482" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="482" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A482" s="3">
         <v>45305</v>
       </c>
@@ -4284,7 +4290,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="483" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="483" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A483" s="3">
         <v>45306</v>
       </c>
@@ -4292,7 +4298,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="484" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="484" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A484" s="3">
         <v>45307</v>
       </c>
@@ -4300,7 +4306,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="485" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="485" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A485" s="3">
         <v>45308</v>
       </c>
@@ -4308,7 +4314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="486" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="486" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A486" s="3">
         <v>45309</v>
       </c>
@@ -4316,7 +4322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="487" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="487" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A487" s="3">
         <v>45310</v>
       </c>
@@ -4324,7 +4330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="488" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="488" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A488" s="3">
         <v>45311</v>
       </c>
@@ -4332,7 +4338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="489" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="489" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A489" s="3">
         <v>45312</v>
       </c>
@@ -4340,7 +4346,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="490" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="490" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A490" s="3">
         <v>45313</v>
       </c>
@@ -4348,7 +4354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="491" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="491" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A491" s="3">
         <v>45314</v>
       </c>
@@ -4356,7 +4362,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="492" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="492" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A492" s="3">
         <v>45315</v>
       </c>
@@ -4364,7 +4370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="493" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="493" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A493" s="3">
         <v>45316</v>
       </c>
@@ -4372,7 +4378,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="494" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="494" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A494" s="3">
         <v>45317</v>
       </c>
@@ -4380,7 +4386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="495" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="495" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A495" s="3">
         <v>45318</v>
       </c>
@@ -4388,7 +4394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="496" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="496" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A496" s="3">
         <v>45319</v>
       </c>
@@ -4396,7 +4402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="497" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="497" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A497" s="3">
         <v>45320</v>
       </c>
@@ -4404,7 +4410,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="498" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="498" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A498" s="3">
         <v>45321</v>
       </c>
@@ -4412,7 +4418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="499" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="499" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A499" s="3">
         <v>45322</v>
       </c>
@@ -4420,7 +4426,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="500" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="500" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A500" s="3">
         <v>45323</v>
       </c>
@@ -4428,7 +4434,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="501" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="501" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A501" s="3">
         <v>45324</v>
       </c>
@@ -4436,7 +4442,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="502" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="502" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A502" s="3">
         <v>45325</v>
       </c>
@@ -4444,7 +4450,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="503" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="503" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A503" s="3">
         <v>45326</v>
       </c>
@@ -4452,7 +4458,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="504" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="504" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A504" s="3">
         <v>45327</v>
       </c>
@@ -4460,7 +4466,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="505" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="505" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A505" s="3">
         <v>45328</v>
       </c>
@@ -4468,7 +4474,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="506" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="506" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A506" s="3">
         <v>45329</v>
       </c>
@@ -4476,7 +4482,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="507" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="507" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A507" s="3">
         <v>45330</v>
       </c>
@@ -4484,7 +4490,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="508" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="508" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A508" s="3">
         <v>45331</v>
       </c>
@@ -4492,7 +4498,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="509" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="509" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A509" s="3">
         <v>45332</v>
       </c>
@@ -4500,7 +4506,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="510" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="510" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A510" s="3">
         <v>45333</v>
       </c>
@@ -4508,7 +4514,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="511" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="511" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A511" s="3">
         <v>45334</v>
       </c>
@@ -4516,7 +4522,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="512" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="512" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A512" s="3">
         <v>45335</v>
       </c>
@@ -4524,7 +4530,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="513" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="513" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A513" s="3">
         <v>45336</v>
       </c>
@@ -4532,7 +4538,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="514" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="514" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A514" s="3">
         <v>45337</v>
       </c>
@@ -4540,7 +4546,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="515" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="515" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A515" s="3">
         <v>45338</v>
       </c>
@@ -4548,7 +4554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="516" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="516" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A516" s="3">
         <v>45339</v>
       </c>
@@ -4556,7 +4562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="517" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="517" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A517" s="3">
         <v>45340</v>
       </c>
@@ -4564,7 +4570,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="518" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="518" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A518" s="3">
         <v>45341</v>
       </c>
@@ -4572,7 +4578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="519" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="519" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A519" s="3">
         <v>45342</v>
       </c>
@@ -4580,7 +4586,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="520" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="520" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A520" s="3">
         <v>45343</v>
       </c>
@@ -4588,7 +4594,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="521" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="521" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A521" s="3">
         <v>45344</v>
       </c>
@@ -4596,7 +4602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="522" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="522" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A522" s="3">
         <v>45345</v>
       </c>
@@ -4604,7 +4610,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="523" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="523" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A523" s="3">
         <v>45346</v>
       </c>
@@ -4612,7 +4618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="524" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="524" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A524" s="3">
         <v>45347</v>
       </c>
@@ -4620,7 +4626,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="525" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="525" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A525" s="3">
         <v>45348</v>
       </c>
@@ -4628,7 +4634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="526" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="526" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A526" s="3">
         <v>45349</v>
       </c>
@@ -4636,7 +4642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="527" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="527" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A527" s="3">
         <v>45350</v>
       </c>
@@ -4644,7 +4650,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="528" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="528" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A528" s="3">
         <v>45351</v>
       </c>
@@ -4652,7 +4658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="529" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="529" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A529" s="3">
         <v>45352</v>
       </c>
@@ -4660,7 +4666,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="530" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="530" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A530" s="3">
         <v>45353</v>
       </c>
@@ -4668,7 +4674,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="531" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="531" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A531" s="3">
         <v>45354</v>
       </c>
@@ -4676,7 +4682,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="532" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="532" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A532" s="3">
         <v>45355</v>
       </c>
@@ -4684,7 +4690,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="533" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="533" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A533" s="3">
         <v>45356</v>
       </c>
@@ -4692,7 +4698,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="534" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="534" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A534" s="3">
         <v>45357</v>
       </c>
@@ -4700,7 +4706,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="535" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="535" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A535" s="3">
         <v>45358</v>
       </c>
@@ -4708,7 +4714,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="536" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="536" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A536" s="3">
         <v>45359</v>
       </c>
@@ -4716,7 +4722,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="537" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="537" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A537" s="3">
         <v>45360</v>
       </c>
@@ -4724,7 +4730,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="538" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="538" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A538" s="3">
         <v>45361</v>
       </c>
@@ -4732,7 +4738,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="539" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="539" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A539" s="3">
         <v>45362</v>
       </c>
@@ -4740,7 +4746,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="540" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="540" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A540" s="3">
         <v>45363</v>
       </c>
@@ -4748,7 +4754,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="541" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="541" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A541" s="3">
         <v>45364</v>
       </c>
@@ -4756,7 +4762,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="542" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="542" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A542" s="3">
         <v>45365</v>
       </c>
@@ -4764,7 +4770,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="543" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="543" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A543" s="3">
         <v>45366</v>
       </c>
@@ -4772,7 +4778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="544" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="544" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A544" s="3">
         <v>45367</v>
       </c>
@@ -4780,7 +4786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="545" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="545" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A545" s="3">
         <v>45368</v>
       </c>
@@ -4788,7 +4794,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="546" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="546" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A546" s="3">
         <v>45369</v>
       </c>
@@ -4796,7 +4802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="547" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="547" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A547" s="3">
         <v>45370</v>
       </c>
@@ -4804,7 +4810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="548" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="548" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A548" s="3">
         <v>45371</v>
       </c>
@@ -4812,7 +4818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="549" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="549" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A549" s="3">
         <v>45372</v>
       </c>
@@ -4820,7 +4826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="550" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="550" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A550" s="3">
         <v>45373</v>
       </c>
@@ -4828,7 +4834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="551" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="551" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A551" s="3">
         <v>45374</v>
       </c>
@@ -4836,7 +4842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="552" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="552" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A552" s="3">
         <v>45375</v>
       </c>
@@ -4844,7 +4850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="553" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="553" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A553" s="3">
         <v>45376</v>
       </c>
@@ -4852,11 +4858,3611 @@
         <v>0</v>
       </c>
     </row>
-    <row r="554" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="554" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A554" s="3">
         <v>45377</v>
       </c>
       <c r="B554" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="555" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A555" s="4">
+        <v>45378</v>
+      </c>
+      <c r="B555" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="556" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A556" s="4">
+        <v>45379</v>
+      </c>
+      <c r="B556" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="557" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A557" s="4">
+        <v>45380</v>
+      </c>
+      <c r="B557" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="558" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A558" s="4">
+        <v>45381</v>
+      </c>
+      <c r="B558" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="559" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A559" s="4">
+        <v>45382</v>
+      </c>
+      <c r="B559" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="560" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A560" s="4">
+        <v>45383</v>
+      </c>
+      <c r="B560" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="561" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A561" s="4">
+        <v>45384</v>
+      </c>
+      <c r="B561" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="562" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A562" s="4">
+        <v>45385</v>
+      </c>
+      <c r="B562" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="563" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A563" s="4">
+        <v>45386</v>
+      </c>
+      <c r="B563" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="564" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A564" s="4">
+        <v>45387</v>
+      </c>
+      <c r="B564" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="565" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A565" s="4">
+        <v>45388</v>
+      </c>
+      <c r="B565" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="566" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A566" s="4">
+        <v>45389</v>
+      </c>
+      <c r="B566" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="567" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A567" s="4">
+        <v>45390</v>
+      </c>
+      <c r="B567" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="568" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A568" s="4">
+        <v>45391</v>
+      </c>
+      <c r="B568" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="569" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A569" s="4">
+        <v>45392</v>
+      </c>
+      <c r="B569" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="570" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A570" s="4">
+        <v>45393</v>
+      </c>
+      <c r="B570" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="571" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A571" s="4">
+        <v>45394</v>
+      </c>
+      <c r="B571" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="572" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A572" s="4">
+        <v>45395</v>
+      </c>
+      <c r="B572" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="573" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A573" s="4">
+        <v>45396</v>
+      </c>
+      <c r="B573" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="574" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A574" s="4">
+        <v>45397</v>
+      </c>
+      <c r="B574" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="575" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A575" s="4">
+        <v>45398</v>
+      </c>
+      <c r="B575" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="576" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A576" s="4">
+        <v>45399</v>
+      </c>
+      <c r="B576" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="577" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A577" s="4">
+        <v>45400</v>
+      </c>
+      <c r="B577" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="578" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A578" s="4">
+        <v>45401</v>
+      </c>
+      <c r="B578" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="579" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A579" s="4">
+        <v>45402</v>
+      </c>
+      <c r="B579" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="580" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A580" s="4">
+        <v>45403</v>
+      </c>
+      <c r="B580" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="581" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A581" s="4">
+        <v>45404</v>
+      </c>
+      <c r="B581" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="582" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A582" s="4">
+        <v>45405</v>
+      </c>
+      <c r="B582" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="583" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A583" s="4">
+        <v>45406</v>
+      </c>
+      <c r="B583" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="584" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A584" s="4">
+        <v>45407</v>
+      </c>
+      <c r="B584" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="585" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A585" s="4">
+        <v>45408</v>
+      </c>
+      <c r="B585" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="586" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A586" s="4">
+        <v>45409</v>
+      </c>
+      <c r="B586" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="587" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A587" s="4">
+        <v>45410</v>
+      </c>
+      <c r="B587" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="588" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A588" s="4">
+        <v>45411</v>
+      </c>
+      <c r="B588" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="589" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A589" s="4">
+        <v>45412</v>
+      </c>
+      <c r="B589" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="590" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A590" s="4">
+        <v>45413</v>
+      </c>
+      <c r="B590" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="591" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A591" s="4">
+        <v>45414</v>
+      </c>
+      <c r="B591" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="592" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A592" s="4">
+        <v>45415</v>
+      </c>
+      <c r="B592" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="593" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A593" s="4">
+        <v>45416</v>
+      </c>
+      <c r="B593" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="594" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A594" s="4">
+        <v>45417</v>
+      </c>
+      <c r="B594" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="595" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A595" s="4">
+        <v>45418</v>
+      </c>
+      <c r="B595" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="596" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A596" s="4">
+        <v>45419</v>
+      </c>
+      <c r="B596" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="597" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A597" s="4">
+        <v>45420</v>
+      </c>
+      <c r="B597" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="598" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A598" s="4">
+        <v>45421</v>
+      </c>
+      <c r="B598" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="599" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A599" s="4">
+        <v>45422</v>
+      </c>
+      <c r="B599" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="600" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A600" s="4">
+        <v>45423</v>
+      </c>
+      <c r="B600" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="601" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A601" s="4">
+        <v>45424</v>
+      </c>
+      <c r="B601" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="602" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A602" s="4">
+        <v>45425</v>
+      </c>
+      <c r="B602" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="603" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A603" s="4">
+        <v>45426</v>
+      </c>
+      <c r="B603" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="604" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A604" s="4">
+        <v>45427</v>
+      </c>
+      <c r="B604" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="605" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A605" s="4">
+        <v>45428</v>
+      </c>
+      <c r="B605" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="606" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A606" s="4">
+        <v>45429</v>
+      </c>
+      <c r="B606" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="607" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A607" s="4">
+        <v>45430</v>
+      </c>
+      <c r="B607" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="608" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A608" s="4">
+        <v>45431</v>
+      </c>
+      <c r="B608" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="609" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A609" s="4">
+        <v>45432</v>
+      </c>
+      <c r="B609" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="610" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A610" s="4">
+        <v>45433</v>
+      </c>
+      <c r="B610" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="611" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A611" s="4">
+        <v>45434</v>
+      </c>
+      <c r="B611" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="612" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A612" s="4">
+        <v>45435</v>
+      </c>
+      <c r="B612" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="613" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A613" s="4">
+        <v>45436</v>
+      </c>
+      <c r="B613" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="614" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A614" s="4">
+        <v>45437</v>
+      </c>
+      <c r="B614" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="615" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A615" s="4">
+        <v>45438</v>
+      </c>
+      <c r="B615" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="616" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A616" s="4">
+        <v>45439</v>
+      </c>
+      <c r="B616" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="617" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A617" s="4">
+        <v>45440</v>
+      </c>
+      <c r="B617" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="618" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A618" s="4">
+        <v>45441</v>
+      </c>
+      <c r="B618" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="619" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A619" s="4">
+        <v>45442</v>
+      </c>
+      <c r="B619" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="620" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A620" s="4">
+        <v>45443</v>
+      </c>
+      <c r="B620" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="621" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A621" s="4">
+        <v>45444</v>
+      </c>
+      <c r="B621" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="622" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A622" s="4">
+        <v>45445</v>
+      </c>
+      <c r="B622" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="623" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A623" s="4">
+        <v>45446</v>
+      </c>
+      <c r="B623" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="624" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A624" s="4">
+        <v>45447</v>
+      </c>
+      <c r="B624" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="625" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A625" s="4">
+        <v>45448</v>
+      </c>
+      <c r="B625" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="626" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A626" s="4">
+        <v>45449</v>
+      </c>
+      <c r="B626" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="627" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A627" s="4">
+        <v>45450</v>
+      </c>
+      <c r="B627" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="628" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A628" s="4">
+        <v>45451</v>
+      </c>
+      <c r="B628" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="629" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A629" s="4">
+        <v>45452</v>
+      </c>
+      <c r="B629" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="630" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A630" s="4">
+        <v>45453</v>
+      </c>
+      <c r="B630" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="631" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A631" s="4">
+        <v>45454</v>
+      </c>
+      <c r="B631" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="632" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A632" s="4">
+        <v>45455</v>
+      </c>
+      <c r="B632" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="633" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A633" s="4">
+        <v>45456</v>
+      </c>
+      <c r="B633" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="634" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A634" s="4">
+        <v>45457</v>
+      </c>
+      <c r="B634" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="635" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A635" s="4">
+        <v>45458</v>
+      </c>
+      <c r="B635" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="636" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A636" s="4">
+        <v>45459</v>
+      </c>
+      <c r="B636" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="637" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A637" s="4">
+        <v>45460</v>
+      </c>
+      <c r="B637" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="638" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A638" s="4">
+        <v>45461</v>
+      </c>
+      <c r="B638" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="639" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A639" s="4">
+        <v>45462</v>
+      </c>
+      <c r="B639" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="640" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A640" s="4">
+        <v>45463</v>
+      </c>
+      <c r="B640" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="641" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A641" s="4">
+        <v>45464</v>
+      </c>
+      <c r="B641" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="642" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A642" s="4">
+        <v>45465</v>
+      </c>
+      <c r="B642" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="643" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A643" s="4">
+        <v>45466</v>
+      </c>
+      <c r="B643" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="644" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A644" s="4">
+        <v>45467</v>
+      </c>
+      <c r="B644" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="645" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A645" s="4">
+        <v>45468</v>
+      </c>
+      <c r="B645" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="646" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A646" s="4">
+        <v>45469</v>
+      </c>
+      <c r="B646" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="647" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A647" s="4">
+        <v>45470</v>
+      </c>
+      <c r="B647" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="648" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A648" s="4">
+        <v>45471</v>
+      </c>
+      <c r="B648" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="649" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A649" s="4">
+        <v>45472</v>
+      </c>
+      <c r="B649" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="650" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A650" s="4">
+        <v>45473</v>
+      </c>
+      <c r="B650" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="651" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A651" s="4">
+        <v>45474</v>
+      </c>
+      <c r="B651" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="652" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A652" s="4">
+        <v>45475</v>
+      </c>
+      <c r="B652" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="653" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A653" s="4">
+        <v>45476</v>
+      </c>
+      <c r="B653" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="654" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A654" s="4">
+        <v>45477</v>
+      </c>
+      <c r="B654" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="655" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A655" s="4">
+        <v>45478</v>
+      </c>
+      <c r="B655" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="656" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A656" s="4">
+        <v>45479</v>
+      </c>
+      <c r="B656" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="657" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A657" s="4">
+        <v>45480</v>
+      </c>
+      <c r="B657" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="658" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A658" s="4">
+        <v>45481</v>
+      </c>
+      <c r="B658" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="659" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A659" s="4">
+        <v>45482</v>
+      </c>
+      <c r="B659" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="660" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A660" s="4">
+        <v>45483</v>
+      </c>
+      <c r="B660" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="661" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A661" s="4">
+        <v>45484</v>
+      </c>
+      <c r="B661" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="662" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A662" s="4">
+        <v>45485</v>
+      </c>
+      <c r="B662" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="663" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A663" s="4">
+        <v>45486</v>
+      </c>
+      <c r="B663" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="664" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A664" s="4">
+        <v>45487</v>
+      </c>
+      <c r="B664" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="665" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A665" s="4">
+        <v>45488</v>
+      </c>
+      <c r="B665" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="666" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A666" s="4">
+        <v>45489</v>
+      </c>
+      <c r="B666" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="667" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A667" s="4">
+        <v>45490</v>
+      </c>
+      <c r="B667" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="668" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A668" s="4">
+        <v>45491</v>
+      </c>
+      <c r="B668" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="669" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A669" s="4">
+        <v>45492</v>
+      </c>
+      <c r="B669" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="670" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A670" s="4">
+        <v>45493</v>
+      </c>
+      <c r="B670" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="671" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A671" s="4">
+        <v>45494</v>
+      </c>
+      <c r="B671" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="672" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A672" s="4">
+        <v>45495</v>
+      </c>
+      <c r="B672" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="673" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A673" s="4">
+        <v>45496</v>
+      </c>
+      <c r="B673" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="674" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A674" s="4">
+        <v>45497</v>
+      </c>
+      <c r="B674" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="675" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A675" s="4">
+        <v>45498</v>
+      </c>
+      <c r="B675" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="676" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A676" s="4">
+        <v>45499</v>
+      </c>
+      <c r="B676" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="677" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A677" s="4">
+        <v>45500</v>
+      </c>
+      <c r="B677" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="678" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A678" s="4">
+        <v>45501</v>
+      </c>
+      <c r="B678" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="679" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A679" s="4">
+        <v>45502</v>
+      </c>
+      <c r="B679" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="680" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A680" s="4">
+        <v>45503</v>
+      </c>
+      <c r="B680" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="681" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A681" s="4">
+        <v>45504</v>
+      </c>
+      <c r="B681" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="682" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A682" s="4">
+        <v>45505</v>
+      </c>
+      <c r="B682" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="683" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A683" s="4">
+        <v>45506</v>
+      </c>
+      <c r="B683" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="684" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A684" s="4">
+        <v>45507</v>
+      </c>
+      <c r="B684" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="685" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A685" s="4">
+        <v>45508</v>
+      </c>
+      <c r="B685" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="686" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A686" s="4">
+        <v>45509</v>
+      </c>
+      <c r="B686" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="687" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A687" s="4">
+        <v>45510</v>
+      </c>
+      <c r="B687" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="688" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A688" s="4">
+        <v>45511</v>
+      </c>
+      <c r="B688" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="689" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A689" s="4">
+        <v>45512</v>
+      </c>
+      <c r="B689" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="690" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A690" s="4">
+        <v>45513</v>
+      </c>
+      <c r="B690" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="691" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A691" s="4">
+        <v>45514</v>
+      </c>
+      <c r="B691" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="692" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A692" s="4">
+        <v>45515</v>
+      </c>
+      <c r="B692" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="693" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A693" s="4">
+        <v>45516</v>
+      </c>
+      <c r="B693" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="694" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A694" s="4">
+        <v>45517</v>
+      </c>
+      <c r="B694" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="695" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A695" s="4">
+        <v>45518</v>
+      </c>
+      <c r="B695" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="696" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A696" s="4">
+        <v>45519</v>
+      </c>
+      <c r="B696" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="697" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A697" s="4">
+        <v>45520</v>
+      </c>
+      <c r="B697" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="698" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A698" s="4">
+        <v>45521</v>
+      </c>
+      <c r="B698" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="699" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A699" s="4">
+        <v>45522</v>
+      </c>
+      <c r="B699" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="700" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A700" s="4">
+        <v>45523</v>
+      </c>
+      <c r="B700" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="701" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A701" s="4">
+        <v>45524</v>
+      </c>
+      <c r="B701" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="702" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A702" s="4">
+        <v>45525</v>
+      </c>
+      <c r="B702" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="703" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A703" s="4">
+        <v>45526</v>
+      </c>
+      <c r="B703" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="704" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A704" s="4">
+        <v>45527</v>
+      </c>
+      <c r="B704" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="705" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A705" s="4">
+        <v>45528</v>
+      </c>
+      <c r="B705" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="706" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A706" s="4">
+        <v>45529</v>
+      </c>
+      <c r="B706" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="707" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A707" s="4">
+        <v>45530</v>
+      </c>
+      <c r="B707" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="708" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A708" s="4">
+        <v>45531</v>
+      </c>
+      <c r="B708" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="709" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A709" s="4">
+        <v>45532</v>
+      </c>
+      <c r="B709" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="710" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A710" s="4">
+        <v>45533</v>
+      </c>
+      <c r="B710" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="711" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A711" s="4">
+        <v>45534</v>
+      </c>
+      <c r="B711" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="712" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A712" s="4">
+        <v>45535</v>
+      </c>
+      <c r="B712" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="713" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A713" s="4">
+        <v>45536</v>
+      </c>
+      <c r="B713" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="714" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A714" s="4">
+        <v>45537</v>
+      </c>
+      <c r="B714" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="715" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A715" s="4">
+        <v>45538</v>
+      </c>
+      <c r="B715" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="716" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A716" s="4">
+        <v>45539</v>
+      </c>
+      <c r="B716" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="717" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A717" s="4">
+        <v>45540</v>
+      </c>
+      <c r="B717" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="718" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A718" s="4">
+        <v>45541</v>
+      </c>
+      <c r="B718" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="719" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A719" s="4">
+        <v>45542</v>
+      </c>
+      <c r="B719" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="720" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A720" s="4">
+        <v>45543</v>
+      </c>
+      <c r="B720" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="721" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A721" s="4">
+        <v>45544</v>
+      </c>
+      <c r="B721" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="722" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A722" s="4">
+        <v>45545</v>
+      </c>
+      <c r="B722" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="723" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A723" s="4">
+        <v>45546</v>
+      </c>
+      <c r="B723" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="724" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A724" s="4">
+        <v>45547</v>
+      </c>
+      <c r="B724" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="725" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A725" s="4">
+        <v>45548</v>
+      </c>
+      <c r="B725" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="726" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A726" s="4">
+        <v>45549</v>
+      </c>
+      <c r="B726" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="727" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A727" s="4">
+        <v>45550</v>
+      </c>
+      <c r="B727" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="728" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A728" s="4">
+        <v>45551</v>
+      </c>
+      <c r="B728" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="729" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A729" s="4">
+        <v>45552</v>
+      </c>
+      <c r="B729" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="730" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A730" s="4">
+        <v>45553</v>
+      </c>
+      <c r="B730" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="731" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A731" s="4">
+        <v>45554</v>
+      </c>
+      <c r="B731" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="732" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A732" s="4">
+        <v>45555</v>
+      </c>
+      <c r="B732" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="733" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A733" s="4">
+        <v>45556</v>
+      </c>
+      <c r="B733" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="734" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A734" s="4">
+        <v>45557</v>
+      </c>
+      <c r="B734" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="735" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A735" s="4">
+        <v>45558</v>
+      </c>
+      <c r="B735" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="736" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A736" s="4">
+        <v>45559</v>
+      </c>
+      <c r="B736" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="737" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A737" s="4">
+        <v>45560</v>
+      </c>
+      <c r="B737" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="738" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A738" s="4">
+        <v>45561</v>
+      </c>
+      <c r="B738" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="739" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A739" s="4">
+        <v>45562</v>
+      </c>
+      <c r="B739" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="740" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A740" s="4">
+        <v>45563</v>
+      </c>
+      <c r="B740" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="741" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A741" s="4">
+        <v>45564</v>
+      </c>
+      <c r="B741" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="742" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A742" s="4">
+        <v>45565</v>
+      </c>
+      <c r="B742" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="743" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A743" s="4">
+        <v>45566</v>
+      </c>
+      <c r="B743" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="744" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A744" s="4">
+        <v>45567</v>
+      </c>
+      <c r="B744" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="745" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A745" s="4">
+        <v>45568</v>
+      </c>
+      <c r="B745" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="746" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A746" s="4">
+        <v>45569</v>
+      </c>
+      <c r="B746" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="747" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A747" s="4">
+        <v>45570</v>
+      </c>
+      <c r="B747" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="748" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A748" s="4">
+        <v>45571</v>
+      </c>
+      <c r="B748" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="749" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A749" s="4">
+        <v>45572</v>
+      </c>
+      <c r="B749" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="750" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A750" s="4">
+        <v>45573</v>
+      </c>
+      <c r="B750" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="751" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A751" s="4">
+        <v>45574</v>
+      </c>
+      <c r="B751" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="752" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A752" s="4">
+        <v>45575</v>
+      </c>
+      <c r="B752" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="753" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A753" s="4">
+        <v>45576</v>
+      </c>
+      <c r="B753" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="754" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A754" s="4">
+        <v>45577</v>
+      </c>
+      <c r="B754" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="755" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A755" s="4">
+        <v>45578</v>
+      </c>
+      <c r="B755" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="756" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A756" s="4">
+        <v>45579</v>
+      </c>
+      <c r="B756" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="757" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A757" s="4">
+        <v>45580</v>
+      </c>
+      <c r="B757" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="758" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A758" s="4">
+        <v>45581</v>
+      </c>
+      <c r="B758" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="759" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A759" s="4">
+        <v>45582</v>
+      </c>
+      <c r="B759" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="760" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A760" s="4">
+        <v>45583</v>
+      </c>
+      <c r="B760" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="761" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A761" s="4">
+        <v>45584</v>
+      </c>
+      <c r="B761" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="762" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A762" s="4">
+        <v>45585</v>
+      </c>
+      <c r="B762" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="763" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A763" s="4">
+        <v>45586</v>
+      </c>
+      <c r="B763" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="764" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A764" s="4">
+        <v>45587</v>
+      </c>
+      <c r="B764" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="765" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A765" s="4">
+        <v>45588</v>
+      </c>
+      <c r="B765" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="766" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A766" s="4">
+        <v>45589</v>
+      </c>
+      <c r="B766" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="767" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A767" s="4">
+        <v>45590</v>
+      </c>
+      <c r="B767" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="768" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A768" s="4">
+        <v>45591</v>
+      </c>
+      <c r="B768" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="769" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A769" s="4">
+        <v>45592</v>
+      </c>
+      <c r="B769" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="770" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A770" s="4">
+        <v>45593</v>
+      </c>
+      <c r="B770" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="771" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A771" s="4">
+        <v>45594</v>
+      </c>
+      <c r="B771" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="772" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A772" s="4">
+        <v>45595</v>
+      </c>
+      <c r="B772" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="773" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A773" s="4">
+        <v>45596</v>
+      </c>
+      <c r="B773" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="774" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A774" s="4">
+        <v>45597</v>
+      </c>
+      <c r="B774" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="775" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A775" s="4">
+        <v>45598</v>
+      </c>
+      <c r="B775" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="776" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A776" s="4">
+        <v>45599</v>
+      </c>
+      <c r="B776" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="777" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A777" s="4">
+        <v>45600</v>
+      </c>
+      <c r="B777" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="778" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A778" s="4">
+        <v>45601</v>
+      </c>
+      <c r="B778" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="779" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A779" s="4">
+        <v>45602</v>
+      </c>
+      <c r="B779" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="780" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A780" s="4">
+        <v>45603</v>
+      </c>
+      <c r="B780" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="781" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A781" s="4">
+        <v>45604</v>
+      </c>
+      <c r="B781" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="782" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A782" s="4">
+        <v>45605</v>
+      </c>
+      <c r="B782" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="783" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A783" s="4">
+        <v>45606</v>
+      </c>
+      <c r="B783" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="784" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A784" s="4">
+        <v>45607</v>
+      </c>
+      <c r="B784" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="785" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A785" s="4">
+        <v>45608</v>
+      </c>
+      <c r="B785" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="786" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A786" s="4">
+        <v>45609</v>
+      </c>
+      <c r="B786" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="787" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A787" s="4">
+        <v>45610</v>
+      </c>
+      <c r="B787" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="788" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A788" s="4">
+        <v>45611</v>
+      </c>
+      <c r="B788" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="789" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A789" s="4">
+        <v>45612</v>
+      </c>
+      <c r="B789" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="790" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A790" s="4">
+        <v>45613</v>
+      </c>
+      <c r="B790" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="791" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A791" s="4">
+        <v>45614</v>
+      </c>
+      <c r="B791" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="792" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A792" s="4">
+        <v>45615</v>
+      </c>
+      <c r="B792" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="793" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A793" s="4">
+        <v>45616</v>
+      </c>
+      <c r="B793" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="794" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A794" s="4">
+        <v>45617</v>
+      </c>
+      <c r="B794" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="795" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A795" s="4">
+        <v>45618</v>
+      </c>
+      <c r="B795" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="796" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A796" s="4">
+        <v>45619</v>
+      </c>
+      <c r="B796" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="797" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A797" s="4">
+        <v>45620</v>
+      </c>
+      <c r="B797" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="798" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A798" s="4">
+        <v>45621</v>
+      </c>
+      <c r="B798" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="799" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A799" s="4">
+        <v>45622</v>
+      </c>
+      <c r="B799" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="800" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A800" s="4">
+        <v>45623</v>
+      </c>
+      <c r="B800" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="801" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A801" s="4">
+        <v>45624</v>
+      </c>
+      <c r="B801" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="802" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A802" s="4">
+        <v>45625</v>
+      </c>
+      <c r="B802" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="803" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A803" s="4">
+        <v>45626</v>
+      </c>
+      <c r="B803" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="804" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A804" s="4">
+        <v>45627</v>
+      </c>
+      <c r="B804" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="805" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A805" s="4">
+        <v>45628</v>
+      </c>
+      <c r="B805" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="806" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A806" s="4">
+        <v>45629</v>
+      </c>
+      <c r="B806" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="807" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A807" s="4">
+        <v>45630</v>
+      </c>
+      <c r="B807" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="808" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A808" s="4">
+        <v>45631</v>
+      </c>
+      <c r="B808" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="809" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A809" s="4">
+        <v>45632</v>
+      </c>
+      <c r="B809" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="810" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A810" s="4">
+        <v>45633</v>
+      </c>
+      <c r="B810" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="811" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A811" s="4">
+        <v>45634</v>
+      </c>
+      <c r="B811" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="812" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A812" s="4">
+        <v>45635</v>
+      </c>
+      <c r="B812" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="813" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A813" s="4">
+        <v>45636</v>
+      </c>
+      <c r="B813" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="814" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A814" s="4">
+        <v>45637</v>
+      </c>
+      <c r="B814" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="815" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A815" s="4">
+        <v>45638</v>
+      </c>
+      <c r="B815" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="816" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A816" s="4">
+        <v>45639</v>
+      </c>
+      <c r="B816" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="817" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A817" s="4">
+        <v>45640</v>
+      </c>
+      <c r="B817" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="818" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A818" s="4">
+        <v>45641</v>
+      </c>
+      <c r="B818" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="819" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A819" s="4">
+        <v>45642</v>
+      </c>
+      <c r="B819" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="820" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A820" s="4">
+        <v>45643</v>
+      </c>
+      <c r="B820" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="821" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A821" s="4">
+        <v>45644</v>
+      </c>
+      <c r="B821" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="822" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A822" s="4">
+        <v>45645</v>
+      </c>
+      <c r="B822" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="823" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A823" s="4">
+        <v>45646</v>
+      </c>
+      <c r="B823" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="824" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A824" s="4">
+        <v>45647</v>
+      </c>
+      <c r="B824" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="825" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A825" s="4">
+        <v>45648</v>
+      </c>
+      <c r="B825" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="826" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A826" s="4">
+        <v>45649</v>
+      </c>
+      <c r="B826" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="827" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A827" s="4">
+        <v>45650</v>
+      </c>
+      <c r="B827" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="828" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A828" s="4">
+        <v>45651</v>
+      </c>
+      <c r="B828" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="829" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A829" s="4">
+        <v>45652</v>
+      </c>
+      <c r="B829" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="830" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A830" s="4">
+        <v>45653</v>
+      </c>
+      <c r="B830" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="831" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A831" s="4">
+        <v>45654</v>
+      </c>
+      <c r="B831" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="832" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A832" s="4">
+        <v>45655</v>
+      </c>
+      <c r="B832" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="833" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A833" s="4">
+        <v>45656</v>
+      </c>
+      <c r="B833" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="834" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A834" s="4">
+        <v>45657</v>
+      </c>
+      <c r="B834" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="835" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B835" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="836" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B836" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="837" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B837" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="838" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B838" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="839" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B839" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="840" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B840" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="841" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B841" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="842" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B842" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="843" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B843" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="844" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B844" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="845" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B845" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="846" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B846" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="847" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B847" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="848" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B848" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="849" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B849" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="850" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B850" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="851" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B851" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="852" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B852" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="853" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B853" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="854" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B854" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="855" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B855" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="856" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B856" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="857" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B857" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="858" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B858" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="859" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B859" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="860" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B860" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="861" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B861" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="862" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B862" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="863" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B863" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="864" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B864" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="865" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B865" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="866" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B866" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="867" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B867" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="868" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B868" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="869" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B869" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="870" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B870" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="871" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B871" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="872" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B872" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="873" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B873" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="874" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B874" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="875" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B875" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="876" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B876" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="877" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B877" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="878" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B878" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="879" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B879" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="880" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B880" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="881" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B881" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="882" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B882" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="883" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B883" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="884" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B884" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="885" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B885" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="886" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B886" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="887" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B887" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="888" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B888" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="889" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B889" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="890" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B890" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="891" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B891" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="892" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B892" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="893" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B893" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="894" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B894" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="895" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B895" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="896" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B896" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="897" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B897" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="898" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B898" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="899" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B899" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="900" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B900" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="901" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B901" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="902" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B902" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="903" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B903" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="904" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B904" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="905" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B905" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="906" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B906" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="907" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B907" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="908" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B908" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="909" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B909" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="910" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B910" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="911" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B911" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="912" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B912" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="913" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B913" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="914" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B914" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="915" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B915" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="916" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B916" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="917" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B917" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="918" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B918" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="919" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B919" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="920" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B920" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="921" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B921" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="922" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B922" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="923" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B923" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="924" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B924" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="925" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B925" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="926" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B926" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="927" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B927" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="928" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B928" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="929" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B929" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="930" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B930" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="931" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B931" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="932" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B932" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="933" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B933" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="934" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B934" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="935" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B935" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="936" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B936" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="937" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B937" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="938" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B938" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="939" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B939" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="940" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B940" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="941" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B941" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="942" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B942" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="943" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B943" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="944" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B944" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="945" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B945" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="946" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B946" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="947" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B947" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="948" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B948" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="949" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B949" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="950" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B950" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="951" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B951" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="952" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B952" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="953" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B953" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="954" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B954" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="955" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B955" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="956" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B956" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="957" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B957" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="958" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B958" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="959" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B959" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="960" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B960" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="961" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B961" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="962" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B962" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="963" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B963" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="964" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B964" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="965" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B965" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="966" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B966" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="967" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B967" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="968" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B968" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="969" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B969" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="970" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B970" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="971" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B971" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="972" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B972" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="973" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B973" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="974" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B974" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="975" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B975" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="976" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B976" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="977" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B977" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="978" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B978" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="979" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B979" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="980" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B980" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="981" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B981" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="982" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B982" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="983" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B983" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="984" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B984" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="985" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B985" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="986" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B986" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="987" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B987" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="988" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B988" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="989" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B989" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="990" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B990" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="991" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B991" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="992" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B992" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="993" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B993" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="994" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B994" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="995" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B995" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="996" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B996" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="997" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B997" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="998" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B998" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="999" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B999" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1000" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1000" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1001" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1001" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1002" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1002" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1003" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1003" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1004" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1004" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1005" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1005" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1006" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1006" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1007" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1007" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1008" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1008" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1009" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1009" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1010" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1010" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1011" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1011" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1012" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1012" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1013" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1013" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1014" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1014" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1015" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1015" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1016" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1016" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1017" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1017" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1018" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1018" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1019" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1019" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1020" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1020" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1021" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1021" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1022" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1022" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1023" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1023" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1024" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1024" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1025" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1025" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1026" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1026" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1027" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1027" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1028" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1028" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1029" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1029" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1030" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1030" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1031" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1031" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1032" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1032" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1033" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1033" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1034" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1034" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1035" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1035" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1036" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1036" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1037" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1037" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1038" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1038" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1039" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1039" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1040" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1040" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1041" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1041" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1042" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1042" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1043" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1043" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1044" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1044" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1045" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1045" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1046" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1046" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1047" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1047" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1048" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1048" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1049" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1049" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1050" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1050" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1051" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1051" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1052" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1052" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1053" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1053" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1054" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1054" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1055" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1055" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1056" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1056" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1057" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1057" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1058" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1058" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1059" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1059" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1060" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1060" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1061" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1061" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1062" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1062" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1063" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1063" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1064" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1064" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1065" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1065" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1066" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1066" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1067" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1067" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1068" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1068" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1069" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1069" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1070" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1070" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1071" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1071" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1072" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1072" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1073" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1073" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1074" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1074" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1075" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1075" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1076" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1076" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1077" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1077" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1078" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1078" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1079" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1079" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1080" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1080" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1081" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1081" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1082" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1082" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1083" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1083" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1084" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1084" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1085" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1085" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1086" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1086" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1087" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1087" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1088" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1088" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1089" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1089" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1090" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1090" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1091" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1091" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1092" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1092" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1093" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1093" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1094" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1094" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1095" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1095" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1096" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1096" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1097" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1097" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1098" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1098" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1099" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1099" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1100" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1100" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1101" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1101" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1102" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1102" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1103" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1103" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1104" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1104" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1105" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1105" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1106" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B1106" s="5">
         <v>0</v>
       </c>
     </row>
